--- a/Données/bord.xlsx
+++ b/Données/bord.xlsx
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -824,7 +824,7 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
@@ -839,7 +839,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
@@ -854,7 +854,7 @@
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -869,7 +869,7 @@
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
@@ -896,7 +896,7 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
         <v>0</v>
@@ -905,7 +905,7 @@
         <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
         <v>0</v>
@@ -914,7 +914,7 @@
         <v>0</v>
       </c>
       <c r="BH2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
@@ -1083,7 +1083,7 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
         <v>0</v>
@@ -1092,7 +1092,7 @@
         <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
         <v>0</v>
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
@@ -1162,13 +1162,13 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1222,7 +1222,7 @@
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
@@ -1279,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="BH4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1454,7 +1454,7 @@
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
         <v>0</v>
@@ -1463,10 +1463,10 @@
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
         <v>0</v>
@@ -1475,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="BH5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1650,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -1659,10 +1659,10 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BH6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1837,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="BH7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="BH8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="BH9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -2410,7 +2410,7 @@
         <v>0</v>
       </c>
       <c r="BH10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -2597,7 +2597,7 @@
         <v>0</v>
       </c>
       <c r="BH11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -2784,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="BH12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -2971,7 +2971,7 @@
         <v>0</v>
       </c>
       <c r="BH13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -3158,7 +3158,7 @@
         <v>0</v>
       </c>
       <c r="BH14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -3345,7 +3345,7 @@
         <v>0</v>
       </c>
       <c r="BH15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -3532,7 +3532,7 @@
         <v>0</v>
       </c>
       <c r="BH16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -3719,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="BH17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -3906,7 +3906,7 @@
         <v>0</v>
       </c>
       <c r="BH18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -4093,7 +4093,7 @@
         <v>0</v>
       </c>
       <c r="BH19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI19" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -4280,7 +4280,7 @@
         <v>0</v>
       </c>
       <c r="BH20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI20" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -4467,7 +4467,7 @@
         <v>0</v>
       </c>
       <c r="BH21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -4654,7 +4654,7 @@
         <v>0</v>
       </c>
       <c r="BH22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI22" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -4841,7 +4841,7 @@
         <v>0</v>
       </c>
       <c r="BH23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI23" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -5028,7 +5028,7 @@
         <v>0</v>
       </c>
       <c r="BH24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI24" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -5215,7 +5215,7 @@
         <v>0</v>
       </c>
       <c r="BH25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI25" t="inlineStr">
         <is>
@@ -5282,7 +5282,7 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -5402,7 +5402,7 @@
         <v>0</v>
       </c>
       <c r="BH26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI26" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5577,7 +5577,7 @@
         <v>0</v>
       </c>
       <c r="BD27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
         <v>0</v>
@@ -5586,10 +5586,10 @@
         <v>0</v>
       </c>
       <c r="BG27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI27" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -5665,7 +5665,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -5773,7 +5773,7 @@
         <v>0</v>
       </c>
       <c r="BG28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BH28" t="n">
         <v>0</v>
@@ -8762,7 +8762,7 @@
         <v>0</v>
       </c>
       <c r="BF44" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -8949,7 +8949,7 @@
         <v>0</v>
       </c>
       <c r="BF45" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9040,7 +9040,7 @@
         <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -9055,7 +9055,7 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
         <v>0</v>
@@ -9118,25 +9118,25 @@
         <v>0</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA46" t="n">
         <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD46" t="n">
         <v>0</v>
       </c>
       <c r="BE46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF46" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9227,7 +9227,7 @@
         <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -9239,10 +9239,10 @@
         <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
         <v>0</v>
@@ -9254,10 +9254,10 @@
         <v>0</v>
       </c>
       <c r="AI47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
         <v>0</v>
       </c>
       <c r="AN47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
@@ -9311,7 +9311,7 @@
         <v>0</v>
       </c>
       <c r="BB47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC47" t="n">
         <v>0</v>
@@ -9320,7 +9320,7 @@
         <v>0</v>
       </c>
       <c r="BE47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF47" t="n">
         <v>0</v>
@@ -9414,7 +9414,7 @@
         <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
         <v>0</v>
@@ -9441,10 +9441,10 @@
         <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
         <v>0</v>
@@ -9456,7 +9456,7 @@
         <v>0</v>
       </c>
       <c r="AN48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
@@ -9492,25 +9492,25 @@
         <v>0</v>
       </c>
       <c r="AZ48" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA48" t="n">
         <v>0</v>
       </c>
       <c r="BB48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC48" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD48" t="n">
         <v>0</v>
       </c>
       <c r="BE48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF48" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -9628,7 +9628,7 @@
         <v>0</v>
       </c>
       <c r="AI49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ49" t="n">
         <v>0</v>
@@ -9643,7 +9643,7 @@
         <v>0</v>
       </c>
       <c r="AN49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
@@ -9685,7 +9685,7 @@
         <v>0</v>
       </c>
       <c r="BB49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC49" t="n">
         <v>0</v>
@@ -9694,7 +9694,7 @@
         <v>0</v>
       </c>
       <c r="BE49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF49" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
         <v>0</v>
       </c>
       <c r="AI50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ50" t="n">
         <v>0</v>
@@ -9830,7 +9830,7 @@
         <v>0</v>
       </c>
       <c r="AN50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
@@ -9872,7 +9872,7 @@
         <v>0</v>
       </c>
       <c r="BB50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC50" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="BE50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF50" t="n">
         <v>0</v>
@@ -9890,7 +9890,7 @@
         <v>0</v>
       </c>
       <c r="BH50" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI50" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>0</v>
       </c>
       <c r="AI51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ51" t="n">
         <v>0</v>
@@ -10017,7 +10017,7 @@
         <v>0</v>
       </c>
       <c r="AN51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
@@ -10059,7 +10059,7 @@
         <v>0</v>
       </c>
       <c r="BB51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC51" t="n">
         <v>0</v>
@@ -10068,7 +10068,7 @@
         <v>0</v>
       </c>
       <c r="BE51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF51" t="n">
         <v>0</v>
@@ -10189,7 +10189,7 @@
         <v>0</v>
       </c>
       <c r="AI52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ52" t="n">
         <v>0</v>
@@ -10204,7 +10204,7 @@
         <v>0</v>
       </c>
       <c r="AN52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
@@ -10246,7 +10246,7 @@
         <v>0</v>
       </c>
       <c r="BB52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC52" t="n">
         <v>0</v>
@@ -10255,7 +10255,7 @@
         <v>0</v>
       </c>
       <c r="BE52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF52" t="n">
         <v>0</v>
@@ -10376,7 +10376,7 @@
         <v>0</v>
       </c>
       <c r="AI53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ53" t="n">
         <v>0</v>
@@ -10391,7 +10391,7 @@
         <v>0</v>
       </c>
       <c r="AN53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
@@ -10433,7 +10433,7 @@
         <v>0</v>
       </c>
       <c r="BB53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC53" t="n">
         <v>0</v>
@@ -10442,7 +10442,7 @@
         <v>0</v>
       </c>
       <c r="BE53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF53" t="n">
         <v>0</v>
@@ -10563,7 +10563,7 @@
         <v>0</v>
       </c>
       <c r="AI54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ54" t="n">
         <v>0</v>
@@ -10578,7 +10578,7 @@
         <v>0</v>
       </c>
       <c r="AN54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO54" t="n">
         <v>0</v>
@@ -10620,7 +10620,7 @@
         <v>0</v>
       </c>
       <c r="BB54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC54" t="n">
         <v>0</v>
@@ -10629,7 +10629,7 @@
         <v>0</v>
       </c>
       <c r="BE54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF54" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
         <v>0</v>
@@ -10750,7 +10750,7 @@
         <v>0</v>
       </c>
       <c r="AI55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ55" t="n">
         <v>0</v>
@@ -10765,7 +10765,7 @@
         <v>0</v>
       </c>
       <c r="AN55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO55" t="n">
         <v>0</v>
@@ -10807,7 +10807,7 @@
         <v>0</v>
       </c>
       <c r="BB55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC55" t="n">
         <v>0</v>
@@ -10816,7 +10816,7 @@
         <v>0</v>
       </c>
       <c r="BE55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF55" t="n">
         <v>0</v>
@@ -10895,7 +10895,7 @@
         <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
         <v>0</v>
@@ -10907,7 +10907,7 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
         <v>0</v>
@@ -10937,10 +10937,10 @@
         <v>0</v>
       </c>
       <c r="AI56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ56" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK56" t="n">
         <v>0</v>
@@ -10952,7 +10952,7 @@
         <v>0</v>
       </c>
       <c r="AN56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO56" t="n">
         <v>0</v>
@@ -10994,7 +10994,7 @@
         <v>0</v>
       </c>
       <c r="BB56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC56" t="n">
         <v>0</v>
@@ -11003,7 +11003,7 @@
         <v>0</v>
       </c>
       <c r="BE56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF56" t="n">
         <v>0</v>
@@ -11094,7 +11094,7 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
         <v>0</v>
@@ -11124,7 +11124,7 @@
         <v>0</v>
       </c>
       <c r="AI57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ57" t="n">
         <v>0</v>
@@ -11139,7 +11139,7 @@
         <v>0</v>
       </c>
       <c r="AN57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO57" t="n">
         <v>0</v>
@@ -11181,7 +11181,7 @@
         <v>0</v>
       </c>
       <c r="BB57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC57" t="n">
         <v>0</v>
@@ -11190,7 +11190,7 @@
         <v>0</v>
       </c>
       <c r="BE57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF57" t="n">
         <v>0</v>
@@ -11281,7 +11281,7 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
         <v>0</v>
@@ -11311,7 +11311,7 @@
         <v>0</v>
       </c>
       <c r="AI58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ58" t="n">
         <v>0</v>
@@ -11326,7 +11326,7 @@
         <v>0</v>
       </c>
       <c r="AN58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO58" t="n">
         <v>0</v>
@@ -11368,7 +11368,7 @@
         <v>0</v>
       </c>
       <c r="BB58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC58" t="n">
         <v>0</v>
@@ -11377,7 +11377,7 @@
         <v>0</v>
       </c>
       <c r="BE58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF58" t="n">
         <v>0</v>
@@ -11468,7 +11468,7 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
         <v>0</v>
@@ -11498,7 +11498,7 @@
         <v>0</v>
       </c>
       <c r="AI59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ59" t="n">
         <v>0</v>
@@ -11513,7 +11513,7 @@
         <v>0</v>
       </c>
       <c r="AN59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO59" t="n">
         <v>0</v>
@@ -11555,7 +11555,7 @@
         <v>0</v>
       </c>
       <c r="BB59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC59" t="n">
         <v>0</v>
@@ -11564,7 +11564,7 @@
         <v>0</v>
       </c>
       <c r="BE59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF59" t="n">
         <v>0</v>
@@ -11655,7 +11655,7 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
         <v>0</v>
@@ -11685,7 +11685,7 @@
         <v>0</v>
       </c>
       <c r="AI60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ60" t="n">
         <v>0</v>
@@ -11700,7 +11700,7 @@
         <v>0</v>
       </c>
       <c r="AN60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO60" t="n">
         <v>0</v>
@@ -11742,7 +11742,7 @@
         <v>0</v>
       </c>
       <c r="BB60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC60" t="n">
         <v>0</v>
@@ -11751,7 +11751,7 @@
         <v>0</v>
       </c>
       <c r="BE60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF60" t="n">
         <v>0</v>
@@ -11842,7 +11842,7 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
         <v>0</v>
@@ -11872,7 +11872,7 @@
         <v>0</v>
       </c>
       <c r="AI61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ61" t="n">
         <v>0</v>
@@ -11887,7 +11887,7 @@
         <v>0</v>
       </c>
       <c r="AN61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO61" t="n">
         <v>0</v>
@@ -11929,7 +11929,7 @@
         <v>0</v>
       </c>
       <c r="BB61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC61" t="n">
         <v>0</v>
@@ -11938,7 +11938,7 @@
         <v>0</v>
       </c>
       <c r="BE61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF61" t="n">
         <v>0</v>
@@ -12029,7 +12029,7 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
         <v>0</v>
@@ -12059,7 +12059,7 @@
         <v>0</v>
       </c>
       <c r="AI62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ62" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="AN62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO62" t="n">
         <v>0</v>
@@ -12116,7 +12116,7 @@
         <v>0</v>
       </c>
       <c r="BB62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC62" t="n">
         <v>0</v>
@@ -12125,7 +12125,7 @@
         <v>0</v>
       </c>
       <c r="BE62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF62" t="n">
         <v>0</v>
@@ -12216,7 +12216,7 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
         <v>0</v>
@@ -12246,7 +12246,7 @@
         <v>0</v>
       </c>
       <c r="AI63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ63" t="n">
         <v>0</v>
@@ -12261,7 +12261,7 @@
         <v>0</v>
       </c>
       <c r="AN63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO63" t="n">
         <v>0</v>
@@ -12303,25 +12303,25 @@
         <v>0</v>
       </c>
       <c r="BB63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC63" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD63" t="n">
         <v>0</v>
       </c>
       <c r="BE63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG63" t="n">
         <v>0</v>
       </c>
       <c r="BH63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI63" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
         <v>0</v>
@@ -12433,7 +12433,7 @@
         <v>0</v>
       </c>
       <c r="AI64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ64" t="n">
         <v>0</v>
@@ -12448,7 +12448,7 @@
         <v>0</v>
       </c>
       <c r="AN64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO64" t="n">
         <v>0</v>
@@ -12490,7 +12490,7 @@
         <v>0</v>
       </c>
       <c r="BB64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC64" t="n">
         <v>0</v>
@@ -12499,7 +12499,7 @@
         <v>0</v>
       </c>
       <c r="BE64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF64" t="n">
         <v>0</v>
@@ -12508,7 +12508,7 @@
         <v>0</v>
       </c>
       <c r="BH64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI64" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
         <v>0</v>
@@ -12620,7 +12620,7 @@
         <v>0</v>
       </c>
       <c r="AI65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ65" t="n">
         <v>0</v>
@@ -12635,7 +12635,7 @@
         <v>0</v>
       </c>
       <c r="AN65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO65" t="n">
         <v>0</v>
@@ -12677,7 +12677,7 @@
         <v>0</v>
       </c>
       <c r="BB65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC65" t="n">
         <v>0</v>
@@ -12686,7 +12686,7 @@
         <v>0</v>
       </c>
       <c r="BE65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF65" t="n">
         <v>0</v>
@@ -12695,7 +12695,7 @@
         <v>0</v>
       </c>
       <c r="BH65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI65" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
         <v>0</v>
@@ -12807,7 +12807,7 @@
         <v>0</v>
       </c>
       <c r="AI66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ66" t="n">
         <v>0</v>
@@ -12822,7 +12822,7 @@
         <v>0</v>
       </c>
       <c r="AN66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO66" t="n">
         <v>0</v>
@@ -12864,7 +12864,7 @@
         <v>0</v>
       </c>
       <c r="BB66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC66" t="n">
         <v>0</v>
@@ -12873,7 +12873,7 @@
         <v>0</v>
       </c>
       <c r="BE66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF66" t="n">
         <v>0</v>
@@ -12882,7 +12882,7 @@
         <v>0</v>
       </c>
       <c r="BH66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI66" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
         <v>0</v>
@@ -12994,7 +12994,7 @@
         <v>0</v>
       </c>
       <c r="AI67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ67" t="n">
         <v>0</v>
@@ -13009,7 +13009,7 @@
         <v>0</v>
       </c>
       <c r="AN67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO67" t="n">
         <v>0</v>
@@ -13051,7 +13051,7 @@
         <v>0</v>
       </c>
       <c r="BB67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC67" t="n">
         <v>0</v>
@@ -13060,7 +13060,7 @@
         <v>0</v>
       </c>
       <c r="BE67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF67" t="n">
         <v>0</v>
@@ -13069,7 +13069,7 @@
         <v>0</v>
       </c>
       <c r="BH67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI67" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
@@ -13181,7 +13181,7 @@
         <v>0</v>
       </c>
       <c r="AI68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ68" t="n">
         <v>0</v>
@@ -13196,7 +13196,7 @@
         <v>0</v>
       </c>
       <c r="AN68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO68" t="n">
         <v>0</v>
@@ -13238,7 +13238,7 @@
         <v>0</v>
       </c>
       <c r="BB68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC68" t="n">
         <v>0</v>
@@ -13247,7 +13247,7 @@
         <v>0</v>
       </c>
       <c r="BE68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF68" t="n">
         <v>0</v>
@@ -13256,7 +13256,7 @@
         <v>0</v>
       </c>
       <c r="BH68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI68" t="inlineStr">
         <is>
@@ -13338,7 +13338,7 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
         <v>0</v>
@@ -13368,7 +13368,7 @@
         <v>0</v>
       </c>
       <c r="AI69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ69" t="n">
         <v>0</v>
@@ -13383,7 +13383,7 @@
         <v>0</v>
       </c>
       <c r="AN69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO69" t="n">
         <v>0</v>
@@ -13425,7 +13425,7 @@
         <v>0</v>
       </c>
       <c r="BB69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC69" t="n">
         <v>0</v>
@@ -13434,7 +13434,7 @@
         <v>0</v>
       </c>
       <c r="BE69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF69" t="n">
         <v>0</v>
@@ -13443,7 +13443,7 @@
         <v>0</v>
       </c>
       <c r="BH69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI69" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
         <v>0</v>
@@ -13555,7 +13555,7 @@
         <v>0</v>
       </c>
       <c r="AI70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ70" t="n">
         <v>0</v>
@@ -13570,7 +13570,7 @@
         <v>0</v>
       </c>
       <c r="AN70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO70" t="n">
         <v>0</v>
@@ -13612,7 +13612,7 @@
         <v>0</v>
       </c>
       <c r="BB70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC70" t="n">
         <v>0</v>
@@ -13621,7 +13621,7 @@
         <v>0</v>
       </c>
       <c r="BE70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF70" t="n">
         <v>0</v>
@@ -13630,7 +13630,7 @@
         <v>0</v>
       </c>
       <c r="BH70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI70" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
         <v>0</v>
@@ -13742,7 +13742,7 @@
         <v>0</v>
       </c>
       <c r="AI71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ71" t="n">
         <v>0</v>
@@ -13757,7 +13757,7 @@
         <v>0</v>
       </c>
       <c r="AN71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO71" t="n">
         <v>0</v>
@@ -13799,7 +13799,7 @@
         <v>0</v>
       </c>
       <c r="BB71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC71" t="n">
         <v>0</v>
@@ -13808,7 +13808,7 @@
         <v>0</v>
       </c>
       <c r="BE71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF71" t="n">
         <v>0</v>
@@ -13817,7 +13817,7 @@
         <v>0</v>
       </c>
       <c r="BH71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI71" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -13929,7 +13929,7 @@
         <v>0</v>
       </c>
       <c r="AI72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ72" t="n">
         <v>0</v>
@@ -13944,7 +13944,7 @@
         <v>0</v>
       </c>
       <c r="AN72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO72" t="n">
         <v>0</v>
@@ -13986,7 +13986,7 @@
         <v>0</v>
       </c>
       <c r="BB72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC72" t="n">
         <v>0</v>
@@ -13995,7 +13995,7 @@
         <v>0</v>
       </c>
       <c r="BE72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF72" t="n">
         <v>0</v>
@@ -14004,7 +14004,7 @@
         <v>0</v>
       </c>
       <c r="BH72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI72" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
         <v>0</v>
@@ -14116,7 +14116,7 @@
         <v>0</v>
       </c>
       <c r="AI73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ73" t="n">
         <v>0</v>
@@ -14131,7 +14131,7 @@
         <v>0</v>
       </c>
       <c r="AN73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO73" t="n">
         <v>0</v>
@@ -14173,7 +14173,7 @@
         <v>0</v>
       </c>
       <c r="BB73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC73" t="n">
         <v>0</v>
@@ -14182,7 +14182,7 @@
         <v>0</v>
       </c>
       <c r="BE73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF73" t="n">
         <v>0</v>
@@ -14191,7 +14191,7 @@
         <v>0</v>
       </c>
       <c r="BH73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI73" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
         <v>0</v>
@@ -14303,7 +14303,7 @@
         <v>0</v>
       </c>
       <c r="AI74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ74" t="n">
         <v>0</v>
@@ -14318,7 +14318,7 @@
         <v>0</v>
       </c>
       <c r="AN74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO74" t="n">
         <v>0</v>
@@ -14360,7 +14360,7 @@
         <v>0</v>
       </c>
       <c r="BB74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC74" t="n">
         <v>0</v>
@@ -14369,7 +14369,7 @@
         <v>0</v>
       </c>
       <c r="BE74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF74" t="n">
         <v>0</v>
@@ -14378,7 +14378,7 @@
         <v>0</v>
       </c>
       <c r="BH74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI74" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
         <v>0</v>
@@ -14490,7 +14490,7 @@
         <v>0</v>
       </c>
       <c r="AI75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ75" t="n">
         <v>0</v>
@@ -14505,7 +14505,7 @@
         <v>0</v>
       </c>
       <c r="AN75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO75" t="n">
         <v>0</v>
@@ -14547,7 +14547,7 @@
         <v>0</v>
       </c>
       <c r="BB75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC75" t="n">
         <v>0</v>
@@ -14556,7 +14556,7 @@
         <v>0</v>
       </c>
       <c r="BE75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF75" t="n">
         <v>0</v>
@@ -14565,7 +14565,7 @@
         <v>0</v>
       </c>
       <c r="BH75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI75" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
         <v>0</v>
@@ -14677,7 +14677,7 @@
         <v>0</v>
       </c>
       <c r="AI76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ76" t="n">
         <v>0</v>
@@ -14692,7 +14692,7 @@
         <v>0</v>
       </c>
       <c r="AN76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO76" t="n">
         <v>0</v>
@@ -14734,7 +14734,7 @@
         <v>0</v>
       </c>
       <c r="BB76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC76" t="n">
         <v>0</v>
@@ -14743,7 +14743,7 @@
         <v>0</v>
       </c>
       <c r="BE76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF76" t="n">
         <v>0</v>
@@ -14752,7 +14752,7 @@
         <v>0</v>
       </c>
       <c r="BH76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI76" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
         <v>0</v>
@@ -14864,7 +14864,7 @@
         <v>0</v>
       </c>
       <c r="AI77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ77" t="n">
         <v>0</v>
@@ -14879,7 +14879,7 @@
         <v>0</v>
       </c>
       <c r="AN77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO77" t="n">
         <v>0</v>
@@ -14921,7 +14921,7 @@
         <v>0</v>
       </c>
       <c r="BB77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC77" t="n">
         <v>0</v>
@@ -14930,7 +14930,7 @@
         <v>0</v>
       </c>
       <c r="BE77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF77" t="n">
         <v>0</v>
@@ -14939,7 +14939,7 @@
         <v>0</v>
       </c>
       <c r="BH77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI77" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
         <v>0</v>
@@ -15051,7 +15051,7 @@
         <v>0</v>
       </c>
       <c r="AI78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ78" t="n">
         <v>0</v>
@@ -15066,7 +15066,7 @@
         <v>0</v>
       </c>
       <c r="AN78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO78" t="n">
         <v>0</v>
@@ -15108,7 +15108,7 @@
         <v>0</v>
       </c>
       <c r="BB78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC78" t="n">
         <v>0</v>
@@ -15117,7 +15117,7 @@
         <v>0</v>
       </c>
       <c r="BE78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF78" t="n">
         <v>0</v>
@@ -15126,7 +15126,7 @@
         <v>0</v>
       </c>
       <c r="BH78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI78" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z79" t="n">
         <v>0</v>
@@ -15238,7 +15238,7 @@
         <v>0</v>
       </c>
       <c r="AI79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ79" t="n">
         <v>0</v>
@@ -15253,7 +15253,7 @@
         <v>0</v>
       </c>
       <c r="AN79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO79" t="n">
         <v>0</v>
@@ -15295,7 +15295,7 @@
         <v>0</v>
       </c>
       <c r="BB79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC79" t="n">
         <v>0</v>
@@ -15304,7 +15304,7 @@
         <v>0</v>
       </c>
       <c r="BE79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF79" t="n">
         <v>0</v>
@@ -15313,7 +15313,7 @@
         <v>0</v>
       </c>
       <c r="BH79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI79" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
         <v>0</v>
@@ -15425,7 +15425,7 @@
         <v>0</v>
       </c>
       <c r="AI80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ80" t="n">
         <v>0</v>
@@ -15440,7 +15440,7 @@
         <v>0</v>
       </c>
       <c r="AN80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO80" t="n">
         <v>0</v>
@@ -15482,7 +15482,7 @@
         <v>0</v>
       </c>
       <c r="BB80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC80" t="n">
         <v>0</v>
@@ -15491,7 +15491,7 @@
         <v>0</v>
       </c>
       <c r="BE80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF80" t="n">
         <v>0</v>
@@ -15500,7 +15500,7 @@
         <v>0</v>
       </c>
       <c r="BH80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI80" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
         <v>0</v>
@@ -15612,7 +15612,7 @@
         <v>0</v>
       </c>
       <c r="AI81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ81" t="n">
         <v>0</v>
@@ -15627,7 +15627,7 @@
         <v>0</v>
       </c>
       <c r="AN81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO81" t="n">
         <v>0</v>
@@ -15669,7 +15669,7 @@
         <v>0</v>
       </c>
       <c r="BB81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC81" t="n">
         <v>0</v>
@@ -15678,7 +15678,7 @@
         <v>0</v>
       </c>
       <c r="BE81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF81" t="n">
         <v>0</v>
@@ -15687,7 +15687,7 @@
         <v>0</v>
       </c>
       <c r="BH81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI81" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
         <v>0</v>
@@ -15799,7 +15799,7 @@
         <v>0</v>
       </c>
       <c r="AI82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ82" t="n">
         <v>0</v>
@@ -15814,7 +15814,7 @@
         <v>0</v>
       </c>
       <c r="AN82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO82" t="n">
         <v>0</v>
@@ -15856,7 +15856,7 @@
         <v>0</v>
       </c>
       <c r="BB82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC82" t="n">
         <v>0</v>
@@ -15865,7 +15865,7 @@
         <v>0</v>
       </c>
       <c r="BE82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF82" t="n">
         <v>0</v>
@@ -15874,7 +15874,7 @@
         <v>0</v>
       </c>
       <c r="BH82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI82" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
         <v>0</v>
@@ -15986,7 +15986,7 @@
         <v>0</v>
       </c>
       <c r="AI83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ83" t="n">
         <v>0</v>
@@ -16001,7 +16001,7 @@
         <v>0</v>
       </c>
       <c r="AN83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO83" t="n">
         <v>0</v>
@@ -16043,7 +16043,7 @@
         <v>0</v>
       </c>
       <c r="BB83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC83" t="n">
         <v>0</v>
@@ -16052,7 +16052,7 @@
         <v>0</v>
       </c>
       <c r="BE83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF83" t="n">
         <v>0</v>
@@ -16061,7 +16061,7 @@
         <v>0</v>
       </c>
       <c r="BH83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI83" t="inlineStr">
         <is>
@@ -16143,7 +16143,7 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z84" t="n">
         <v>0</v>
@@ -16173,7 +16173,7 @@
         <v>0</v>
       </c>
       <c r="AI84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ84" t="n">
         <v>0</v>
@@ -16188,7 +16188,7 @@
         <v>0</v>
       </c>
       <c r="AN84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO84" t="n">
         <v>0</v>
@@ -16230,7 +16230,7 @@
         <v>0</v>
       </c>
       <c r="BB84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC84" t="n">
         <v>0</v>
@@ -16239,7 +16239,7 @@
         <v>0</v>
       </c>
       <c r="BE84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF84" t="n">
         <v>0</v>
@@ -16248,7 +16248,7 @@
         <v>0</v>
       </c>
       <c r="BH84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI84" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
         <v>0</v>
@@ -16360,7 +16360,7 @@
         <v>0</v>
       </c>
       <c r="AI85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ85" t="n">
         <v>0</v>
@@ -16375,7 +16375,7 @@
         <v>0</v>
       </c>
       <c r="AN85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO85" t="n">
         <v>0</v>
@@ -16417,7 +16417,7 @@
         <v>0</v>
       </c>
       <c r="BB85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC85" t="n">
         <v>0</v>
@@ -16426,7 +16426,7 @@
         <v>0</v>
       </c>
       <c r="BE85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF85" t="n">
         <v>0</v>
@@ -16435,7 +16435,7 @@
         <v>0</v>
       </c>
       <c r="BH85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI85" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
         <v>0</v>
@@ -16541,13 +16541,13 @@
         <v>0</v>
       </c>
       <c r="AG86" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH86" t="n">
         <v>0</v>
       </c>
       <c r="AI86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ86" t="n">
         <v>0</v>
@@ -16562,7 +16562,7 @@
         <v>0</v>
       </c>
       <c r="AN86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO86" t="n">
         <v>0</v>
@@ -16604,7 +16604,7 @@
         <v>0</v>
       </c>
       <c r="BB86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC86" t="n">
         <v>0</v>
@@ -16613,7 +16613,7 @@
         <v>0</v>
       </c>
       <c r="BE86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF86" t="n">
         <v>0</v>
@@ -16622,7 +16622,7 @@
         <v>0</v>
       </c>
       <c r="BH86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI86" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
         <v>0</v>
@@ -16728,7 +16728,7 @@
         <v>0</v>
       </c>
       <c r="AG87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH87" t="n">
         <v>0</v>
@@ -16743,7 +16743,7 @@
         <v>0</v>
       </c>
       <c r="AL87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM87" t="n">
         <v>0</v>
@@ -16791,7 +16791,7 @@
         <v>0</v>
       </c>
       <c r="BB87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC87" t="n">
         <v>0</v>
@@ -16800,7 +16800,7 @@
         <v>0</v>
       </c>
       <c r="BE87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF87" t="n">
         <v>0</v>
@@ -16809,7 +16809,7 @@
         <v>0</v>
       </c>
       <c r="BH87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI87" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
         <v>0</v>
@@ -16900,7 +16900,7 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -16978,7 +16978,7 @@
         <v>0</v>
       </c>
       <c r="BB88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC88" t="n">
         <v>0</v>
@@ -16987,7 +16987,7 @@
         <v>0</v>
       </c>
       <c r="BE88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF88" t="n">
         <v>0</v>
@@ -16996,7 +16996,7 @@
         <v>0</v>
       </c>
       <c r="BH88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI88" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="n">
         <v>0</v>
@@ -17165,7 +17165,7 @@
         <v>0</v>
       </c>
       <c r="BB89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC89" t="n">
         <v>0</v>
@@ -17174,7 +17174,7 @@
         <v>0</v>
       </c>
       <c r="BE89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF89" t="n">
         <v>0</v>
@@ -17183,7 +17183,7 @@
         <v>0</v>
       </c>
       <c r="BH89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI89" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
         <v>0</v>
@@ -17352,7 +17352,7 @@
         <v>0</v>
       </c>
       <c r="BB90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC90" t="n">
         <v>0</v>
@@ -17361,7 +17361,7 @@
         <v>0</v>
       </c>
       <c r="BE90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF90" t="n">
         <v>0</v>
@@ -17370,7 +17370,7 @@
         <v>0</v>
       </c>
       <c r="BH90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI90" t="inlineStr">
         <is>
@@ -17452,7 +17452,7 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
         <v>0</v>
@@ -17539,7 +17539,7 @@
         <v>0</v>
       </c>
       <c r="BB91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC91" t="n">
         <v>0</v>
@@ -17548,7 +17548,7 @@
         <v>0</v>
       </c>
       <c r="BE91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF91" t="n">
         <v>0</v>
@@ -17557,7 +17557,7 @@
         <v>0</v>
       </c>
       <c r="BH91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI91" t="inlineStr">
         <is>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
         <v>0</v>
@@ -17654,7 +17654,7 @@
         <v>0</v>
       </c>
       <c r="AD92" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE92" t="n">
         <v>0</v>
@@ -17669,7 +17669,7 @@
         <v>0</v>
       </c>
       <c r="AI92" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ92" t="n">
         <v>0</v>
@@ -17726,7 +17726,7 @@
         <v>0</v>
       </c>
       <c r="BB92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC92" t="n">
         <v>0</v>
@@ -17735,7 +17735,7 @@
         <v>0</v>
       </c>
       <c r="BE92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF92" t="n">
         <v>0</v>
@@ -17744,7 +17744,7 @@
         <v>0</v>
       </c>
       <c r="BH92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI92" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
         <v>0</v>
@@ -17913,7 +17913,7 @@
         <v>0</v>
       </c>
       <c r="BB93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC93" t="n">
         <v>0</v>
@@ -17922,7 +17922,7 @@
         <v>0</v>
       </c>
       <c r="BE93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF93" t="n">
         <v>0</v>
@@ -17931,7 +17931,7 @@
         <v>0</v>
       </c>
       <c r="BH93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI93" t="inlineStr">
         <is>
@@ -18013,7 +18013,7 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
         <v>0</v>
@@ -18100,7 +18100,7 @@
         <v>0</v>
       </c>
       <c r="BB94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC94" t="n">
         <v>0</v>
@@ -18109,7 +18109,7 @@
         <v>0</v>
       </c>
       <c r="BE94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF94" t="n">
         <v>0</v>
@@ -18118,7 +18118,7 @@
         <v>0</v>
       </c>
       <c r="BH94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI94" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
         <v>0</v>
@@ -18287,7 +18287,7 @@
         <v>0</v>
       </c>
       <c r="BB95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC95" t="n">
         <v>0</v>
@@ -18296,7 +18296,7 @@
         <v>0</v>
       </c>
       <c r="BE95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF95" t="n">
         <v>0</v>
@@ -18305,7 +18305,7 @@
         <v>0</v>
       </c>
       <c r="BH95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI95" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
         <v>0</v>
@@ -18474,7 +18474,7 @@
         <v>0</v>
       </c>
       <c r="BB96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC96" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
         <v>0</v>
       </c>
       <c r="BE96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF96" t="n">
         <v>0</v>
@@ -18492,7 +18492,7 @@
         <v>0</v>
       </c>
       <c r="BH96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI96" t="inlineStr">
         <is>
@@ -18574,7 +18574,7 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
         <v>0</v>
@@ -18661,7 +18661,7 @@
         <v>0</v>
       </c>
       <c r="BB97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC97" t="n">
         <v>0</v>
@@ -18670,7 +18670,7 @@
         <v>0</v>
       </c>
       <c r="BE97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF97" t="n">
         <v>0</v>
@@ -18679,7 +18679,7 @@
         <v>0</v>
       </c>
       <c r="BH97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI97" t="inlineStr">
         <is>
@@ -18761,7 +18761,7 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
         <v>0</v>
@@ -18848,7 +18848,7 @@
         <v>0</v>
       </c>
       <c r="BB98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC98" t="n">
         <v>0</v>
@@ -18857,7 +18857,7 @@
         <v>0</v>
       </c>
       <c r="BE98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF98" t="n">
         <v>0</v>
@@ -18866,7 +18866,7 @@
         <v>0</v>
       </c>
       <c r="BH98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI98" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>0</v>
       </c>
       <c r="W99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X99" t="n">
         <v>0</v>
@@ -18987,7 +18987,7 @@
         <v>0</v>
       </c>
       <c r="AL99" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM99" t="n">
         <v>0</v>
@@ -19035,7 +19035,7 @@
         <v>0</v>
       </c>
       <c r="BB99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC99" t="n">
         <v>0</v>
@@ -19044,7 +19044,7 @@
         <v>0</v>
       </c>
       <c r="BE99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF99" t="n">
         <v>0</v>
@@ -19053,7 +19053,7 @@
         <v>0</v>
       </c>
       <c r="BH99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI99" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>0</v>
       </c>
       <c r="BB100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC100" t="n">
         <v>0</v>
@@ -19231,7 +19231,7 @@
         <v>0</v>
       </c>
       <c r="BE100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF100" t="n">
         <v>0</v>
@@ -19240,7 +19240,7 @@
         <v>0</v>
       </c>
       <c r="BH100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI100" t="inlineStr">
         <is>
@@ -19409,7 +19409,7 @@
         <v>0</v>
       </c>
       <c r="BB101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC101" t="n">
         <v>0</v>
@@ -19418,7 +19418,7 @@
         <v>0</v>
       </c>
       <c r="BE101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF101" t="n">
         <v>0</v>
@@ -19427,7 +19427,7 @@
         <v>0</v>
       </c>
       <c r="BH101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI101" t="inlineStr">
         <is>
@@ -19596,7 +19596,7 @@
         <v>0</v>
       </c>
       <c r="BB102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC102" t="n">
         <v>0</v>
@@ -19605,7 +19605,7 @@
         <v>0</v>
       </c>
       <c r="BE102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF102" t="n">
         <v>0</v>
@@ -19614,7 +19614,7 @@
         <v>0</v>
       </c>
       <c r="BH102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI102" t="inlineStr">
         <is>
@@ -19783,7 +19783,7 @@
         <v>0</v>
       </c>
       <c r="BB103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC103" t="n">
         <v>0</v>
@@ -19792,7 +19792,7 @@
         <v>0</v>
       </c>
       <c r="BE103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF103" t="n">
         <v>0</v>
@@ -19801,7 +19801,7 @@
         <v>0</v>
       </c>
       <c r="BH103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI103" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>0</v>
       </c>
       <c r="BB104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC104" t="n">
         <v>0</v>
@@ -19979,7 +19979,7 @@
         <v>0</v>
       </c>
       <c r="BE104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF104" t="n">
         <v>0</v>
@@ -19988,7 +19988,7 @@
         <v>0</v>
       </c>
       <c r="BH104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI104" t="inlineStr">
         <is>
@@ -20157,7 +20157,7 @@
         <v>0</v>
       </c>
       <c r="BB105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC105" t="n">
         <v>0</v>
@@ -20166,7 +20166,7 @@
         <v>0</v>
       </c>
       <c r="BE105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF105" t="n">
         <v>0</v>
@@ -20175,7 +20175,7 @@
         <v>0</v>
       </c>
       <c r="BH105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI105" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>0</v>
       </c>
       <c r="BB106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC106" t="n">
         <v>0</v>
@@ -20353,7 +20353,7 @@
         <v>0</v>
       </c>
       <c r="BE106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF106" t="n">
         <v>0</v>
@@ -20362,7 +20362,7 @@
         <v>0</v>
       </c>
       <c r="BH106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI106" t="inlineStr">
         <is>
@@ -20531,7 +20531,7 @@
         <v>0</v>
       </c>
       <c r="BB107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC107" t="n">
         <v>0</v>
@@ -20540,7 +20540,7 @@
         <v>0</v>
       </c>
       <c r="BE107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF107" t="n">
         <v>0</v>
@@ -20549,7 +20549,7 @@
         <v>0</v>
       </c>
       <c r="BH107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI107" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>0</v>
       </c>
       <c r="BB108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC108" t="n">
         <v>0</v>
@@ -20727,7 +20727,7 @@
         <v>0</v>
       </c>
       <c r="BE108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF108" t="n">
         <v>0</v>
@@ -20736,7 +20736,7 @@
         <v>0</v>
       </c>
       <c r="BH108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI108" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>0</v>
       </c>
       <c r="BB109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC109" t="n">
         <v>0</v>
@@ -20914,7 +20914,7 @@
         <v>0</v>
       </c>
       <c r="BE109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF109" t="n">
         <v>0</v>
@@ -20923,7 +20923,7 @@
         <v>0</v>
       </c>
       <c r="BH109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI109" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>0</v>
       </c>
       <c r="BB110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC110" t="n">
         <v>0</v>
@@ -21101,7 +21101,7 @@
         <v>0</v>
       </c>
       <c r="BE110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF110" t="n">
         <v>0</v>
@@ -21110,7 +21110,7 @@
         <v>0</v>
       </c>
       <c r="BH110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI110" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>0</v>
       </c>
       <c r="BB111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC111" t="n">
         <v>0</v>
@@ -21288,7 +21288,7 @@
         <v>0</v>
       </c>
       <c r="BE111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF111" t="n">
         <v>0</v>
@@ -21297,7 +21297,7 @@
         <v>0</v>
       </c>
       <c r="BH111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI111" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>0</v>
       </c>
       <c r="BB112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC112" t="n">
         <v>0</v>
@@ -21475,7 +21475,7 @@
         <v>0</v>
       </c>
       <c r="BE112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF112" t="n">
         <v>0</v>
@@ -21484,7 +21484,7 @@
         <v>0</v>
       </c>
       <c r="BH112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI112" t="inlineStr">
         <is>
@@ -21653,7 +21653,7 @@
         <v>0</v>
       </c>
       <c r="BB113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC113" t="n">
         <v>0</v>
@@ -21662,7 +21662,7 @@
         <v>0</v>
       </c>
       <c r="BE113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF113" t="n">
         <v>0</v>
@@ -21671,7 +21671,7 @@
         <v>0</v>
       </c>
       <c r="BH113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI113" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>0</v>
       </c>
       <c r="BB114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC114" t="n">
         <v>0</v>
@@ -21849,7 +21849,7 @@
         <v>0</v>
       </c>
       <c r="BE114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF114" t="n">
         <v>0</v>
@@ -21858,7 +21858,7 @@
         <v>0</v>
       </c>
       <c r="BH114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI114" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>0</v>
       </c>
       <c r="BB115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC115" t="n">
         <v>0</v>
@@ -22036,7 +22036,7 @@
         <v>0</v>
       </c>
       <c r="BE115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF115" t="n">
         <v>0</v>
@@ -22045,7 +22045,7 @@
         <v>0</v>
       </c>
       <c r="BH115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI115" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>0</v>
       </c>
       <c r="BB116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC116" t="n">
         <v>0</v>
@@ -22223,7 +22223,7 @@
         <v>0</v>
       </c>
       <c r="BE116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF116" t="n">
         <v>0</v>
@@ -22232,7 +22232,7 @@
         <v>0</v>
       </c>
       <c r="BH116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI116" t="inlineStr">
         <is>
@@ -22287,7 +22287,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
@@ -22299,7 +22299,7 @@
         <v>0</v>
       </c>
       <c r="T117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U117" t="n">
         <v>0</v>
@@ -22401,7 +22401,7 @@
         <v>0</v>
       </c>
       <c r="BB117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC117" t="n">
         <v>0</v>
@@ -22410,7 +22410,7 @@
         <v>0</v>
       </c>
       <c r="BE117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF117" t="n">
         <v>0</v>
@@ -22419,7 +22419,7 @@
         <v>0</v>
       </c>
       <c r="BH117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI117" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>0</v>
       </c>
       <c r="T118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U118" t="n">
         <v>0</v>
@@ -22588,7 +22588,7 @@
         <v>0</v>
       </c>
       <c r="BB118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC118" t="n">
         <v>0</v>
@@ -22597,7 +22597,7 @@
         <v>0</v>
       </c>
       <c r="BE118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF118" t="n">
         <v>0</v>
@@ -22606,7 +22606,7 @@
         <v>0</v>
       </c>
       <c r="BH118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI118" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>0</v>
       </c>
       <c r="T119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U119" t="n">
         <v>0</v>
@@ -22775,7 +22775,7 @@
         <v>0</v>
       </c>
       <c r="BB119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC119" t="n">
         <v>0</v>
@@ -22784,7 +22784,7 @@
         <v>0</v>
       </c>
       <c r="BE119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF119" t="n">
         <v>0</v>
@@ -22793,7 +22793,7 @@
         <v>0</v>
       </c>
       <c r="BH119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI119" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
         <v>0</v>
       </c>
       <c r="T120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U120" t="n">
         <v>0</v>
@@ -22962,7 +22962,7 @@
         <v>0</v>
       </c>
       <c r="BB120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC120" t="n">
         <v>0</v>
@@ -22971,7 +22971,7 @@
         <v>0</v>
       </c>
       <c r="BE120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF120" t="n">
         <v>0</v>
@@ -22980,7 +22980,7 @@
         <v>0</v>
       </c>
       <c r="BH120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI120" t="inlineStr">
         <is>
@@ -23047,7 +23047,7 @@
         <v>0</v>
       </c>
       <c r="T121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U121" t="n">
         <v>0</v>
@@ -23149,7 +23149,7 @@
         <v>0</v>
       </c>
       <c r="BB121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC121" t="n">
         <v>0</v>
@@ -23158,7 +23158,7 @@
         <v>0</v>
       </c>
       <c r="BE121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF121" t="n">
         <v>0</v>
@@ -23167,7 +23167,7 @@
         <v>0</v>
       </c>
       <c r="BH121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI121" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>0</v>
       </c>
       <c r="T122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U122" t="n">
         <v>0</v>
@@ -23336,7 +23336,7 @@
         <v>0</v>
       </c>
       <c r="BB122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC122" t="n">
         <v>0</v>
@@ -23345,7 +23345,7 @@
         <v>0</v>
       </c>
       <c r="BE122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF122" t="n">
         <v>0</v>
@@ -23354,7 +23354,7 @@
         <v>0</v>
       </c>
       <c r="BH122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI122" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>0</v>
       </c>
       <c r="T123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U123" t="n">
         <v>0</v>
@@ -23523,7 +23523,7 @@
         <v>0</v>
       </c>
       <c r="BB123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC123" t="n">
         <v>0</v>
@@ -23532,7 +23532,7 @@
         <v>0</v>
       </c>
       <c r="BE123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF123" t="n">
         <v>0</v>
@@ -23541,7 +23541,7 @@
         <v>0</v>
       </c>
       <c r="BH123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI123" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>0</v>
       </c>
       <c r="T124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U124" t="n">
         <v>0</v>
@@ -23710,7 +23710,7 @@
         <v>0</v>
       </c>
       <c r="BB124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC124" t="n">
         <v>0</v>
@@ -23719,7 +23719,7 @@
         <v>0</v>
       </c>
       <c r="BE124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF124" t="n">
         <v>0</v>
@@ -23728,7 +23728,7 @@
         <v>0</v>
       </c>
       <c r="BH124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI124" t="inlineStr">
         <is>
@@ -23795,7 +23795,7 @@
         <v>0</v>
       </c>
       <c r="T125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U125" t="n">
         <v>0</v>
@@ -23897,7 +23897,7 @@
         <v>0</v>
       </c>
       <c r="BB125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC125" t="n">
         <v>0</v>
@@ -23906,7 +23906,7 @@
         <v>0</v>
       </c>
       <c r="BE125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF125" t="n">
         <v>0</v>
@@ -23915,7 +23915,7 @@
         <v>0</v>
       </c>
       <c r="BH125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI125" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>0</v>
       </c>
       <c r="T126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U126" t="n">
         <v>0</v>
@@ -24084,7 +24084,7 @@
         <v>0</v>
       </c>
       <c r="BB126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC126" t="n">
         <v>0</v>
@@ -24093,7 +24093,7 @@
         <v>0</v>
       </c>
       <c r="BE126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF126" t="n">
         <v>0</v>
@@ -24102,7 +24102,7 @@
         <v>0</v>
       </c>
       <c r="BH126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI126" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>0</v>
       </c>
       <c r="T127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U127" t="n">
         <v>0</v>
@@ -24271,7 +24271,7 @@
         <v>0</v>
       </c>
       <c r="BB127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC127" t="n">
         <v>0</v>
@@ -24280,7 +24280,7 @@
         <v>0</v>
       </c>
       <c r="BE127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF127" t="n">
         <v>0</v>
@@ -24289,7 +24289,7 @@
         <v>0</v>
       </c>
       <c r="BH127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI127" t="inlineStr">
         <is>
@@ -24356,7 +24356,7 @@
         <v>0</v>
       </c>
       <c r="T128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
@@ -24458,7 +24458,7 @@
         <v>0</v>
       </c>
       <c r="BB128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC128" t="n">
         <v>0</v>
@@ -24467,7 +24467,7 @@
         <v>0</v>
       </c>
       <c r="BE128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF128" t="n">
         <v>0</v>
@@ -24476,7 +24476,7 @@
         <v>0</v>
       </c>
       <c r="BH128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI128" t="inlineStr">
         <is>
@@ -24543,7 +24543,7 @@
         <v>0</v>
       </c>
       <c r="T129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
@@ -24645,7 +24645,7 @@
         <v>0</v>
       </c>
       <c r="BB129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC129" t="n">
         <v>0</v>
@@ -24654,7 +24654,7 @@
         <v>0</v>
       </c>
       <c r="BE129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF129" t="n">
         <v>0</v>
@@ -24663,7 +24663,7 @@
         <v>0</v>
       </c>
       <c r="BH129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI129" t="inlineStr">
         <is>
@@ -24730,7 +24730,7 @@
         <v>0</v>
       </c>
       <c r="T130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U130" t="n">
         <v>0</v>
@@ -24832,7 +24832,7 @@
         <v>0</v>
       </c>
       <c r="BB130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC130" t="n">
         <v>0</v>
@@ -24841,7 +24841,7 @@
         <v>0</v>
       </c>
       <c r="BE130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF130" t="n">
         <v>0</v>
@@ -24850,7 +24850,7 @@
         <v>0</v>
       </c>
       <c r="BH130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI130" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         <v>0</v>
       </c>
       <c r="T131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U131" t="n">
         <v>0</v>
@@ -25019,10 +25019,10 @@
         <v>0</v>
       </c>
       <c r="BB131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD131" t="n">
         <v>0</v>
@@ -25037,7 +25037,7 @@
         <v>0</v>
       </c>
       <c r="BH131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI131" t="inlineStr">
         <is>
@@ -25104,7 +25104,7 @@
         <v>0</v>
       </c>
       <c r="T132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U132" t="n">
         <v>0</v>
@@ -25206,7 +25206,7 @@
         <v>0</v>
       </c>
       <c r="BB132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC132" t="n">
         <v>0</v>
@@ -25218,7 +25218,7 @@
         <v>1</v>
       </c>
       <c r="BF132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG132" t="n">
         <v>0</v>
@@ -25291,7 +25291,7 @@
         <v>0</v>
       </c>
       <c r="T133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U133" t="n">
         <v>0</v>
@@ -25387,7 +25387,7 @@
         <v>0</v>
       </c>
       <c r="AZ133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA133" t="n">
         <v>0</v>
@@ -25478,7 +25478,7 @@
         <v>0</v>
       </c>
       <c r="T134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U134" t="n">
         <v>0</v>
@@ -25665,7 +25665,7 @@
         <v>0</v>
       </c>
       <c r="T135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U135" t="n">
         <v>0</v>
@@ -25852,7 +25852,7 @@
         <v>0</v>
       </c>
       <c r="T136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U136" t="n">
         <v>0</v>
@@ -26039,7 +26039,7 @@
         <v>0</v>
       </c>
       <c r="T137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U137" t="n">
         <v>0</v>
@@ -26226,7 +26226,7 @@
         <v>0</v>
       </c>
       <c r="T138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U138" t="n">
         <v>0</v>
@@ -26413,7 +26413,7 @@
         <v>0</v>
       </c>
       <c r="T139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U139" t="n">
         <v>0</v>
@@ -26600,7 +26600,7 @@
         <v>0</v>
       </c>
       <c r="T140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U140" t="n">
         <v>0</v>
@@ -26787,7 +26787,7 @@
         <v>0</v>
       </c>
       <c r="T141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U141" t="n">
         <v>0</v>
@@ -26820,7 +26820,7 @@
         <v>0</v>
       </c>
       <c r="AE141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF141" t="n">
         <v>0</v>
@@ -26832,10 +26832,10 @@
         <v>0</v>
       </c>
       <c r="AI141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK141" t="n">
         <v>0</v>
@@ -26847,7 +26847,7 @@
         <v>0</v>
       </c>
       <c r="AN141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO141" t="n">
         <v>0</v>
@@ -26974,7 +26974,7 @@
         <v>0</v>
       </c>
       <c r="T142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U142" t="n">
         <v>0</v>
@@ -26989,7 +26989,7 @@
         <v>0</v>
       </c>
       <c r="Y142" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z142" t="n">
         <v>0</v>
@@ -27019,7 +27019,7 @@
         <v>0</v>
       </c>
       <c r="AI142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ142" t="n">
         <v>0</v>
@@ -27034,7 +27034,7 @@
         <v>0</v>
       </c>
       <c r="AN142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO142" t="n">
         <v>0</v>
@@ -27161,7 +27161,7 @@
         <v>0</v>
       </c>
       <c r="T143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U143" t="n">
         <v>0</v>
@@ -27206,7 +27206,7 @@
         <v>0</v>
       </c>
       <c r="AI143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ143" t="n">
         <v>0</v>
@@ -27221,7 +27221,7 @@
         <v>0</v>
       </c>
       <c r="AN143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO143" t="n">
         <v>0</v>
@@ -27348,10 +27348,10 @@
         <v>0</v>
       </c>
       <c r="T144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U144" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V144" t="n">
         <v>0</v>
@@ -27363,10 +27363,10 @@
         <v>0</v>
       </c>
       <c r="Y144" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA144" t="n">
         <v>0</v>
@@ -27378,7 +27378,7 @@
         <v>0</v>
       </c>
       <c r="AD144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE144" t="n">
         <v>0</v>
@@ -27393,10 +27393,10 @@
         <v>0</v>
       </c>
       <c r="AI144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ144" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK144" t="n">
         <v>0</v>
@@ -27408,7 +27408,7 @@
         <v>0</v>
       </c>
       <c r="AN144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO144" t="n">
         <v>0</v>
@@ -27535,7 +27535,7 @@
         <v>0</v>
       </c>
       <c r="T145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U145" t="n">
         <v>0</v>
@@ -27565,7 +27565,7 @@
         <v>0</v>
       </c>
       <c r="AD145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE145" t="n">
         <v>0</v>
@@ -27580,7 +27580,7 @@
         <v>0</v>
       </c>
       <c r="AI145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ145" t="n">
         <v>0</v>
@@ -27595,7 +27595,7 @@
         <v>0</v>
       </c>
       <c r="AN145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO145" t="n">
         <v>0</v>
@@ -27722,7 +27722,7 @@
         <v>0</v>
       </c>
       <c r="T146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U146" t="n">
         <v>0</v>
@@ -27752,7 +27752,7 @@
         <v>0</v>
       </c>
       <c r="AD146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE146" t="n">
         <v>0</v>
@@ -27767,7 +27767,7 @@
         <v>0</v>
       </c>
       <c r="AI146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ146" t="n">
         <v>0</v>
@@ -27782,7 +27782,7 @@
         <v>0</v>
       </c>
       <c r="AN146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO146" t="n">
         <v>0</v>
@@ -27909,7 +27909,7 @@
         <v>0</v>
       </c>
       <c r="T147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U147" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
         <v>0</v>
       </c>
       <c r="AD147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE147" t="n">
         <v>0</v>
@@ -27954,7 +27954,7 @@
         <v>0</v>
       </c>
       <c r="AI147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ147" t="n">
         <v>0</v>
@@ -27969,7 +27969,7 @@
         <v>0</v>
       </c>
       <c r="AN147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO147" t="n">
         <v>0</v>
@@ -28096,7 +28096,7 @@
         <v>0</v>
       </c>
       <c r="T148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U148" t="n">
         <v>0</v>
@@ -28126,7 +28126,7 @@
         <v>0</v>
       </c>
       <c r="AD148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE148" t="n">
         <v>0</v>
@@ -28141,7 +28141,7 @@
         <v>0</v>
       </c>
       <c r="AI148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ148" t="n">
         <v>0</v>
@@ -28156,7 +28156,7 @@
         <v>0</v>
       </c>
       <c r="AN148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO148" t="n">
         <v>0</v>
@@ -28283,7 +28283,7 @@
         <v>0</v>
       </c>
       <c r="T149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U149" t="n">
         <v>0</v>
@@ -28313,7 +28313,7 @@
         <v>0</v>
       </c>
       <c r="AD149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE149" t="n">
         <v>0</v>
@@ -28328,7 +28328,7 @@
         <v>0</v>
       </c>
       <c r="AI149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ149" t="n">
         <v>0</v>
@@ -28343,7 +28343,7 @@
         <v>0</v>
       </c>
       <c r="AN149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO149" t="n">
         <v>0</v>
@@ -28470,7 +28470,7 @@
         <v>0</v>
       </c>
       <c r="T150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U150" t="n">
         <v>0</v>
@@ -28500,7 +28500,7 @@
         <v>0</v>
       </c>
       <c r="AD150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE150" t="n">
         <v>0</v>
@@ -28515,7 +28515,7 @@
         <v>0</v>
       </c>
       <c r="AI150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ150" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
         <v>0</v>
       </c>
       <c r="AN150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO150" t="n">
         <v>0</v>
@@ -28657,7 +28657,7 @@
         <v>0</v>
       </c>
       <c r="T151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U151" t="n">
         <v>0</v>
@@ -28687,7 +28687,7 @@
         <v>0</v>
       </c>
       <c r="AD151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE151" t="n">
         <v>0</v>
@@ -28702,7 +28702,7 @@
         <v>0</v>
       </c>
       <c r="AI151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ151" t="n">
         <v>0</v>
@@ -28717,7 +28717,7 @@
         <v>0</v>
       </c>
       <c r="AN151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO151" t="n">
         <v>0</v>
@@ -28844,10 +28844,10 @@
         <v>0</v>
       </c>
       <c r="T152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V152" t="n">
         <v>0</v>
@@ -28859,7 +28859,7 @@
         <v>0</v>
       </c>
       <c r="Y152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z152" t="n">
         <v>0</v>
@@ -28874,7 +28874,7 @@
         <v>0</v>
       </c>
       <c r="AD152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE152" t="n">
         <v>0</v>
@@ -28889,7 +28889,7 @@
         <v>0</v>
       </c>
       <c r="AI152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ152" t="n">
         <v>0</v>
@@ -28904,7 +28904,7 @@
         <v>0</v>
       </c>
       <c r="AN152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO152" t="n">
         <v>0</v>
@@ -29031,7 +29031,7 @@
         <v>0</v>
       </c>
       <c r="T153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U153" t="n">
         <v>0</v>
@@ -29046,7 +29046,7 @@
         <v>0</v>
       </c>
       <c r="Y153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z153" t="n">
         <v>0</v>
@@ -29061,7 +29061,7 @@
         <v>0</v>
       </c>
       <c r="AD153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE153" t="n">
         <v>0</v>
@@ -29076,7 +29076,7 @@
         <v>0</v>
       </c>
       <c r="AI153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ153" t="n">
         <v>0</v>
@@ -29091,7 +29091,7 @@
         <v>0</v>
       </c>
       <c r="AN153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO153" t="n">
         <v>0</v>
@@ -29218,7 +29218,7 @@
         <v>0</v>
       </c>
       <c r="T154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U154" t="n">
         <v>0</v>
@@ -29233,7 +29233,7 @@
         <v>0</v>
       </c>
       <c r="Y154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z154" t="n">
         <v>0</v>
@@ -29248,7 +29248,7 @@
         <v>0</v>
       </c>
       <c r="AD154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE154" t="n">
         <v>0</v>
@@ -29263,7 +29263,7 @@
         <v>0</v>
       </c>
       <c r="AI154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ154" t="n">
         <v>0</v>
@@ -29278,7 +29278,7 @@
         <v>0</v>
       </c>
       <c r="AN154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO154" t="n">
         <v>0</v>
@@ -29405,7 +29405,7 @@
         <v>0</v>
       </c>
       <c r="T155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U155" t="n">
         <v>0</v>
@@ -29420,7 +29420,7 @@
         <v>0</v>
       </c>
       <c r="Y155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z155" t="n">
         <v>0</v>
@@ -29435,7 +29435,7 @@
         <v>0</v>
       </c>
       <c r="AD155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE155" t="n">
         <v>0</v>
@@ -29450,7 +29450,7 @@
         <v>0</v>
       </c>
       <c r="AI155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ155" t="n">
         <v>0</v>
@@ -29465,7 +29465,7 @@
         <v>0</v>
       </c>
       <c r="AN155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO155" t="n">
         <v>0</v>
@@ -29592,7 +29592,7 @@
         <v>0</v>
       </c>
       <c r="T156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U156" t="n">
         <v>0</v>
@@ -29607,7 +29607,7 @@
         <v>0</v>
       </c>
       <c r="Y156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z156" t="n">
         <v>0</v>
@@ -29622,7 +29622,7 @@
         <v>0</v>
       </c>
       <c r="AD156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE156" t="n">
         <v>0</v>
@@ -29637,7 +29637,7 @@
         <v>0</v>
       </c>
       <c r="AI156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ156" t="n">
         <v>0</v>
@@ -29652,7 +29652,7 @@
         <v>0</v>
       </c>
       <c r="AN156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO156" t="n">
         <v>0</v>
@@ -29773,7 +29773,7 @@
         <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -29788,13 +29788,13 @@
         <v>0</v>
       </c>
       <c r="W157" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="X157" t="n">
         <v>0</v>
       </c>
       <c r="Y157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z157" t="n">
         <v>0</v>
@@ -29809,7 +29809,7 @@
         <v>0</v>
       </c>
       <c r="AD157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE157" t="n">
         <v>0</v>
@@ -29824,7 +29824,7 @@
         <v>0</v>
       </c>
       <c r="AI157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ157" t="n">
         <v>0</v>
@@ -29839,7 +29839,7 @@
         <v>0</v>
       </c>
       <c r="AN157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO157" t="n">
         <v>0</v>
@@ -29981,7 +29981,7 @@
         <v>0</v>
       </c>
       <c r="Y158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z158" t="n">
         <v>0</v>
@@ -29996,7 +29996,7 @@
         <v>0</v>
       </c>
       <c r="AD158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE158" t="n">
         <v>0</v>
@@ -30011,7 +30011,7 @@
         <v>0</v>
       </c>
       <c r="AI158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ158" t="n">
         <v>0</v>
@@ -30026,7 +30026,7 @@
         <v>0</v>
       </c>
       <c r="AN158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO158" t="n">
         <v>0</v>
@@ -30168,7 +30168,7 @@
         <v>0</v>
       </c>
       <c r="Y159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z159" t="n">
         <v>0</v>
@@ -30177,13 +30177,13 @@
         <v>0</v>
       </c>
       <c r="AB159" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC159" t="n">
         <v>0</v>
       </c>
       <c r="AD159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE159" t="n">
         <v>0</v>
@@ -30198,7 +30198,7 @@
         <v>0</v>
       </c>
       <c r="AI159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ159" t="n">
         <v>0</v>
@@ -30207,13 +30207,13 @@
         <v>0</v>
       </c>
       <c r="AL159" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM159" t="n">
         <v>0</v>
       </c>
       <c r="AN159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO159" t="n">
         <v>0</v>
@@ -30340,7 +30340,7 @@
         <v>0</v>
       </c>
       <c r="T160" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U160" t="n">
         <v>0</v>
@@ -30355,7 +30355,7 @@
         <v>0</v>
       </c>
       <c r="Y160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z160" t="n">
         <v>0</v>
@@ -30370,7 +30370,7 @@
         <v>0</v>
       </c>
       <c r="AD160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE160" t="n">
         <v>0</v>
@@ -30385,7 +30385,7 @@
         <v>0</v>
       </c>
       <c r="AI160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ160" t="n">
         <v>0</v>
@@ -30400,7 +30400,7 @@
         <v>0</v>
       </c>
       <c r="AN160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO160" t="n">
         <v>0</v>
@@ -30521,7 +30521,7 @@
         <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -30542,7 +30542,7 @@
         <v>0</v>
       </c>
       <c r="Y161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z161" t="n">
         <v>0</v>
@@ -30557,7 +30557,7 @@
         <v>0</v>
       </c>
       <c r="AD161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE161" t="n">
         <v>0</v>
@@ -30566,13 +30566,13 @@
         <v>0</v>
       </c>
       <c r="AG161" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH161" t="n">
         <v>0</v>
       </c>
       <c r="AI161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ161" t="n">
         <v>0</v>
@@ -30587,7 +30587,7 @@
         <v>0</v>
       </c>
       <c r="AN161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO161" t="n">
         <v>0</v>
@@ -30708,13 +30708,13 @@
         <v>0</v>
       </c>
       <c r="R162" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
       </c>
       <c r="T162" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U162" t="n">
         <v>0</v>
@@ -30729,7 +30729,7 @@
         <v>0</v>
       </c>
       <c r="Y162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z162" t="n">
         <v>0</v>
@@ -30744,7 +30744,7 @@
         <v>0</v>
       </c>
       <c r="AD162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE162" t="n">
         <v>0</v>
@@ -30753,13 +30753,13 @@
         <v>0</v>
       </c>
       <c r="AG162" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH162" t="n">
         <v>0</v>
       </c>
       <c r="AI162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ162" t="n">
         <v>0</v>
@@ -30774,7 +30774,7 @@
         <v>0</v>
       </c>
       <c r="AN162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO162" t="n">
         <v>0</v>
@@ -30916,7 +30916,7 @@
         <v>0</v>
       </c>
       <c r="Y163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z163" t="n">
         <v>0</v>
@@ -30931,7 +30931,7 @@
         <v>0</v>
       </c>
       <c r="AD163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE163" t="n">
         <v>0</v>
@@ -30946,7 +30946,7 @@
         <v>0</v>
       </c>
       <c r="AI163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ163" t="n">
         <v>0</v>
@@ -30961,7 +30961,7 @@
         <v>0</v>
       </c>
       <c r="AN163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO163" t="n">
         <v>0</v>
@@ -31103,7 +31103,7 @@
         <v>0</v>
       </c>
       <c r="Y164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z164" t="n">
         <v>0</v>
@@ -31118,7 +31118,7 @@
         <v>0</v>
       </c>
       <c r="AD164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE164" t="n">
         <v>0</v>
@@ -31133,7 +31133,7 @@
         <v>0</v>
       </c>
       <c r="AI164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ164" t="n">
         <v>0</v>
@@ -31148,7 +31148,7 @@
         <v>0</v>
       </c>
       <c r="AN164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO164" t="n">
         <v>0</v>
@@ -31269,13 +31269,13 @@
         <v>0</v>
       </c>
       <c r="R165" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
       </c>
       <c r="T165" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U165" t="n">
         <v>0</v>
@@ -31290,7 +31290,7 @@
         <v>0</v>
       </c>
       <c r="Y165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z165" t="n">
         <v>0</v>
@@ -31305,7 +31305,7 @@
         <v>0</v>
       </c>
       <c r="AD165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE165" t="n">
         <v>0</v>
@@ -31320,7 +31320,7 @@
         <v>0</v>
       </c>
       <c r="AI165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ165" t="n">
         <v>0</v>
@@ -31335,7 +31335,7 @@
         <v>0</v>
       </c>
       <c r="AN165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO165" t="n">
         <v>0</v>
@@ -31471,13 +31471,13 @@
         <v>0</v>
       </c>
       <c r="W166" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="X166" t="n">
         <v>0</v>
       </c>
       <c r="Y166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z166" t="n">
         <v>0</v>
@@ -31492,7 +31492,7 @@
         <v>0</v>
       </c>
       <c r="AD166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE166" t="n">
         <v>0</v>
@@ -31507,7 +31507,7 @@
         <v>0</v>
       </c>
       <c r="AI166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ166" t="n">
         <v>0</v>
@@ -31522,7 +31522,7 @@
         <v>0</v>
       </c>
       <c r="AN166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO166" t="n">
         <v>0</v>
@@ -31658,13 +31658,13 @@
         <v>0</v>
       </c>
       <c r="W167" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="X167" t="n">
         <v>0</v>
       </c>
       <c r="Y167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z167" t="n">
         <v>0</v>
@@ -31679,7 +31679,7 @@
         <v>0</v>
       </c>
       <c r="AD167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE167" t="n">
         <v>0</v>
@@ -31694,7 +31694,7 @@
         <v>0</v>
       </c>
       <c r="AI167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ167" t="n">
         <v>0</v>
@@ -31709,7 +31709,7 @@
         <v>0</v>
       </c>
       <c r="AN167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO167" t="n">
         <v>0</v>
@@ -31851,7 +31851,7 @@
         <v>0</v>
       </c>
       <c r="Y168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z168" t="n">
         <v>0</v>
@@ -31866,7 +31866,7 @@
         <v>0</v>
       </c>
       <c r="AD168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE168" t="n">
         <v>0</v>
@@ -31881,7 +31881,7 @@
         <v>0</v>
       </c>
       <c r="AI168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ168" t="n">
         <v>0</v>
@@ -31896,7 +31896,7 @@
         <v>0</v>
       </c>
       <c r="AN168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO168" t="n">
         <v>0</v>
@@ -31972,13 +31972,13 @@
         <v>0</v>
       </c>
       <c r="C169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D169" t="n">
         <v>0</v>
       </c>
       <c r="E169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F169" t="n">
         <v>0</v>
@@ -31987,13 +31987,13 @@
         <v>0</v>
       </c>
       <c r="H169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I169" t="n">
         <v>0</v>
       </c>
       <c r="J169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K169" t="n">
         <v>0</v>
@@ -32002,13 +32002,13 @@
         <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N169" t="n">
         <v>0</v>
       </c>
       <c r="O169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P169" t="n">
         <v>0</v>
@@ -32038,7 +32038,7 @@
         <v>0</v>
       </c>
       <c r="Y169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z169" t="n">
         <v>0</v>
@@ -32053,7 +32053,7 @@
         <v>0</v>
       </c>
       <c r="AD169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE169" t="n">
         <v>0</v>
@@ -32068,7 +32068,7 @@
         <v>0</v>
       </c>
       <c r="AI169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ169" t="n">
         <v>0</v>
@@ -32083,7 +32083,7 @@
         <v>0</v>
       </c>
       <c r="AN169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO169" t="n">
         <v>0</v>
@@ -32122,28 +32122,28 @@
         <v>0</v>
       </c>
       <c r="BA169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC169" t="n">
         <v>0</v>
       </c>
       <c r="BD169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF169" t="n">
         <v>0</v>
       </c>
       <c r="BG169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI169" t="inlineStr">
         <is>
